--- a/Config/Datas/Tables/s_属性_AttributeConfig.xlsx
+++ b/Config/Datas/Tables/s_属性_AttributeConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbAttribute" sheetId="1" r:id="Re7da06b880bf423e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbAttribute" sheetId="1" r:id="R64fe17bb26224c28"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -62,8 +62,25 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -93,6 +110,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF64748B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF6F8FA"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -162,7 +199,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="45">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -256,6 +293,42 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -462,6 +535,11 @@
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -477,6 +555,21 @@
       <x:c r="D1" s="11" t="str">
         <x:v>displayFormat</x:v>
       </x:c>
+      <x:c r="E1" s="38" t="str">
+        <x:v>attributeType</x:v>
+      </x:c>
+      <x:c r="F1" s="38" t="str">
+        <x:v>valueKind</x:v>
+      </x:c>
+      <x:c r="G1" s="38" t="str">
+        <x:v>unit</x:v>
+      </x:c>
+      <x:c r="H1" s="38" t="str">
+        <x:v>minValue</x:v>
+      </x:c>
+      <x:c r="I1" s="38" t="str">
+        <x:v>maxValue</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="29" t="str">
@@ -491,6 +584,21 @@
       <x:c r="D2" s="14" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="E2" s="40" t="str">
+        <x:v>EAttributeType</x:v>
+      </x:c>
+      <x:c r="F2" s="40" t="str">
+        <x:v>EAttributeValueKind</x:v>
+      </x:c>
+      <x:c r="G2" s="40" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="H2" s="40" t="str">
+        <x:v>double</x:v>
+      </x:c>
+      <x:c r="I2" s="40" t="str">
+        <x:v>double</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="30" t="str">
@@ -499,8 +607,13 @@
       <x:c r="B3" s="16"/>
       <x:c r="C3" s="16"/>
       <x:c r="D3" s="16"/>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="E3" s="41"/>
+      <x:c r="F3" s="41"/>
+      <x:c r="G3" s="41"/>
+      <x:c r="H3" s="41"/>
+      <x:c r="I3" s="41"/>
+    </x:row>
+    <x:row r="4" ht="70" customHeight="1">
       <x:c r="A4" s="31" t="str">
         <x:v>##</x:v>
       </x:c>
@@ -511,11 +624,401 @@
         <x:v>显示名称</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>显示格式；无需求前保持空表</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="B5" s="32"/>
+        <x:v>显示格式；整数与实数按数值类型显示</x:v>
+      </x:c>
+      <x:c r="E4" s="42" t="str">
+        <x:v>属性程序语义</x:v>
+      </x:c>
+      <x:c r="F4" s="42" t="str">
+        <x:v>整数属性在最终聚合时取整</x:v>
+      </x:c>
+      <x:c r="G4" s="42" t="str">
+        <x:v>属性单位</x:v>
+      </x:c>
+      <x:c r="H4" s="42" t="str">
+        <x:v>合法下限；调试值</x:v>
+      </x:c>
+      <x:c r="I4" s="42" t="str">
+        <x:v>合法上限；调试值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="26" customHeight="1">
+      <x:c r="A5" s="34"/>
+      <x:c r="B5" s="44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="34" t="str">
+        <x:v>最大生命</x:v>
+      </x:c>
+      <x:c r="D5" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="36" t="str">
+        <x:v>MaxHealth</x:v>
+      </x:c>
+      <x:c r="F5" s="36" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="G5" s="36" t="str">
+        <x:v>点</x:v>
+      </x:c>
+      <x:c r="H5" s="36" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I5" s="36" t="n">
+        <x:v>1000000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="26" customHeight="1">
+      <x:c r="A6" s="34"/>
+      <x:c r="B6" s="34" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C6" s="34" t="str">
+        <x:v>攻击</x:v>
+      </x:c>
+      <x:c r="D6" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="34" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="F6" s="34" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="G6" s="34" t="str">
+        <x:v>点</x:v>
+      </x:c>
+      <x:c r="H6" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" s="34" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="26" customHeight="1">
+      <x:c r="A7" s="34"/>
+      <x:c r="B7" s="34" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="34" t="str">
+        <x:v>防御</x:v>
+      </x:c>
+      <x:c r="D7" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="34" t="str">
+        <x:v>Defense</x:v>
+      </x:c>
+      <x:c r="F7" s="34" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="G7" s="34" t="str">
+        <x:v>点</x:v>
+      </x:c>
+      <x:c r="H7" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" s="34" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="26" customHeight="1">
+      <x:c r="A8" s="34"/>
+      <x:c r="B8" s="34" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="str">
+        <x:v>移动速度</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="str">
+        <x:v>0.###</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="str">
+        <x:v>MoveSpeed</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="str">
+        <x:v>世界单位每秒</x:v>
+      </x:c>
+      <x:c r="H8" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" s="34" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="26" customHeight="1">
+      <x:c r="A9" s="34"/>
+      <x:c r="B9" s="34" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C9" s="34" t="str">
+        <x:v>攻速倍率</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="str">
+        <x:v>0.###</x:v>
+      </x:c>
+      <x:c r="E9" s="34" t="str">
+        <x:v>AttackSpeedMultiplier</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="str">
+        <x:v>倍率</x:v>
+      </x:c>
+      <x:c r="H9" s="34" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="I9" s="34" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="26" customHeight="1">
+      <x:c r="A10" s="34"/>
+      <x:c r="B10" s="34" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C10" s="34" t="str">
+        <x:v>防御参数</x:v>
+      </x:c>
+      <x:c r="D10" s="34" t="str">
+        <x:v>0.###</x:v>
+      </x:c>
+      <x:c r="E10" s="34" t="str">
+        <x:v>DefenseParameter</x:v>
+      </x:c>
+      <x:c r="F10" s="34" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="G10" s="34" t="str">
+        <x:v>倍率</x:v>
+      </x:c>
+      <x:c r="H10" s="34" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="I10" s="34" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="26" customHeight="1">
+      <x:c r="A11" s="34"/>
+      <x:c r="B11" s="34" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C11" s="34" t="str">
+        <x:v>命中值</x:v>
+      </x:c>
+      <x:c r="D11" s="34" t="str">
+        <x:v>0.###</x:v>
+      </x:c>
+      <x:c r="E11" s="34" t="str">
+        <x:v>Hit</x:v>
+      </x:c>
+      <x:c r="F11" s="34" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="G11" s="34" t="str">
+        <x:v>点</x:v>
+      </x:c>
+      <x:c r="H11" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" s="34" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="26" customHeight="1">
+      <x:c r="A12" s="34"/>
+      <x:c r="B12" s="34" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C12" s="34" t="str">
+        <x:v>闪避值</x:v>
+      </x:c>
+      <x:c r="D12" s="34" t="str">
+        <x:v>0.###</x:v>
+      </x:c>
+      <x:c r="E12" s="34" t="str">
+        <x:v>Evasion</x:v>
+      </x:c>
+      <x:c r="F12" s="34" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="G12" s="34" t="str">
+        <x:v>点</x:v>
+      </x:c>
+      <x:c r="H12" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" s="34" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="26" customHeight="1">
+      <x:c r="A13" s="34"/>
+      <x:c r="B13" s="34" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C13" s="34" t="str">
+        <x:v>命中参数</x:v>
+      </x:c>
+      <x:c r="D13" s="34" t="str">
+        <x:v>0.###</x:v>
+      </x:c>
+      <x:c r="E13" s="34" t="str">
+        <x:v>HitParameter</x:v>
+      </x:c>
+      <x:c r="F13" s="34" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="G13" s="34" t="str">
+        <x:v>倍率</x:v>
+      </x:c>
+      <x:c r="H13" s="34" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="I13" s="34" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="26" customHeight="1">
+      <x:c r="A14" s="34"/>
+      <x:c r="B14" s="34" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C14" s="34" t="str">
+        <x:v>闪避参数</x:v>
+      </x:c>
+      <x:c r="D14" s="34" t="str">
+        <x:v>0.###</x:v>
+      </x:c>
+      <x:c r="E14" s="34" t="str">
+        <x:v>EvasionParameter</x:v>
+      </x:c>
+      <x:c r="F14" s="34" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="G14" s="34" t="str">
+        <x:v>倍率</x:v>
+      </x:c>
+      <x:c r="H14" s="34" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="I14" s="34" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="26" customHeight="1">
+      <x:c r="A15" s="34"/>
+      <x:c r="B15" s="34" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C15" s="34" t="str">
+        <x:v>暴击值</x:v>
+      </x:c>
+      <x:c r="D15" s="34" t="str">
+        <x:v>0.###</x:v>
+      </x:c>
+      <x:c r="E15" s="34" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="F15" s="34" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="G15" s="34" t="str">
+        <x:v>点</x:v>
+      </x:c>
+      <x:c r="H15" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="34" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="26" customHeight="1">
+      <x:c r="A16" s="34"/>
+      <x:c r="B16" s="34" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C16" s="34" t="str">
+        <x:v>抗暴值</x:v>
+      </x:c>
+      <x:c r="D16" s="34" t="str">
+        <x:v>0.###</x:v>
+      </x:c>
+      <x:c r="E16" s="34" t="str">
+        <x:v>CriticalResistance</x:v>
+      </x:c>
+      <x:c r="F16" s="34" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="G16" s="34" t="str">
+        <x:v>点</x:v>
+      </x:c>
+      <x:c r="H16" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" s="34" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="34"/>
+      <x:c r="B17" s="34" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C17" s="34" t="str">
+        <x:v>暴击参数</x:v>
+      </x:c>
+      <x:c r="D17" s="34" t="str">
+        <x:v>0.###</x:v>
+      </x:c>
+      <x:c r="E17" s="34" t="str">
+        <x:v>CriticalParameter</x:v>
+      </x:c>
+      <x:c r="F17" s="34" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="G17" s="34" t="str">
+        <x:v>倍率</x:v>
+      </x:c>
+      <x:c r="H17" s="34" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="I17" s="34" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="34"/>
+      <x:c r="B18" s="34" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="34" t="str">
+        <x:v>抗暴参数</x:v>
+      </x:c>
+      <x:c r="D18" s="34" t="str">
+        <x:v>0.###</x:v>
+      </x:c>
+      <x:c r="E18" s="34" t="str">
+        <x:v>CriticalResistanceParameter</x:v>
+      </x:c>
+      <x:c r="F18" s="34" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="G18" s="34" t="str">
+        <x:v>倍率</x:v>
+      </x:c>
+      <x:c r="H18" s="34" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="I18" s="34" t="n">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
